--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XX/LTAIPT_A63F20.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XX/LTAIPT_A63F20.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842E9A22-9226-4A31-A27B-4B7C9F6E74E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8AFBA7-D32D-4703-BC5D-9C295298ABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="432">
   <si>
     <t>48969</t>
   </si>
@@ -413,88 +413,76 @@
     <t>16347580</t>
   </si>
   <si>
+    <t>9CA0A89471E510702EF6A24BAAB22680</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>15987051</t>
   </si>
   <si>
+    <t>11/10/2024</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de Julio de 2024 al 30 de Septiembre de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no publica información inherente al Plazo con el que cuenta el sujeto obligado para prevenir al solicitante y Plazo con el que cuenta el solicitante para cumplir con la prevención según Artículo 46 Fracción XI de la Ley General de Mejora Regulatoria</t>
+  </si>
+  <si>
+    <t>BB7E5062708FF5B2DFB0FFB3F8E2DAF8</t>
+  </si>
+  <si>
     <t>15987050</t>
   </si>
   <si>
+    <t>6A5CDFAE0E21EA89D0E3090AF07EE862</t>
+  </si>
+  <si>
     <t>15987056</t>
   </si>
   <si>
+    <t>72F150790A731F7EDDAB8E79CAF36EF4</t>
+  </si>
+  <si>
     <t>15987055</t>
   </si>
   <si>
+    <t>E6E600D021F0F235597D7B3D2F4005F3</t>
+  </si>
+  <si>
     <t>15987052</t>
   </si>
   <si>
+    <t>B5FCB6C23147324B8DB170DBEB92172E</t>
+  </si>
+  <si>
     <t>15987054</t>
   </si>
   <si>
+    <t>D6A2BAEF6FBB19F59EFF5E931C6277AD</t>
+  </si>
+  <si>
     <t>15987053</t>
   </si>
   <si>
-    <t>EEBDBE20250758BC52E693A6B7672CD0</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>Estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>14416145</t>
   </si>
   <si>
-    <t>02/07/2024</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de abril de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no publica información inherente al Plazo con el que cuenta el sujeto obligado para prevenir al solicitante y Plazo con el que cuenta el solicitante para cumplir con la prevención según Artículo 46 Fracción XI de la Ley General de Mejora Regulatoria</t>
-  </si>
-  <si>
-    <t>EC5942B42425E9F3FEFBD80C657256CE</t>
-  </si>
-  <si>
-    <t>Estudiantes o ex-estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>14416146</t>
   </si>
   <si>
-    <t>57B2EAC5374A57CE51077CFBB89BB7C3</t>
-  </si>
-  <si>
-    <t>Ex-estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>14416147</t>
   </si>
   <si>
-    <t>56C0456F5B9A7934B010380E1EE3ED4B</t>
-  </si>
-  <si>
-    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>14416148</t>
   </si>
   <si>
-    <t>8B1D5BEC39D6AF07462EE5159D5CA4CF</t>
-  </si>
-  <si>
     <t>14416144</t>
   </si>
   <si>
-    <t>DC210F7427557BC2A13835F00449BDCC</t>
-  </si>
-  <si>
     <t>14416143</t>
-  </si>
-  <si>
-    <t>9478B3A853A1C57652062B9ED4619F98</t>
   </si>
   <si>
     <t>14416142</t>
@@ -2127,25 +2115,25 @@
     </row>
     <row r="8" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>73</v>
@@ -2154,16 +2142,16 @@
         <v>74</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>76</v>
@@ -2172,22 +2160,22 @@
         <v>76</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>83</v>
@@ -2196,10 +2184,10 @@
         <v>76</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>74</v>
@@ -2208,33 +2196,33 @@
         <v>84</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>73</v>
@@ -2243,16 +2231,16 @@
         <v>74</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>76</v>
@@ -2264,19 +2252,19 @@
         <v>78</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>81</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>83</v>
@@ -2285,10 +2273,10 @@
         <v>76</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>74</v>
@@ -2297,33 +2285,33 @@
         <v>84</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>73</v>
@@ -2332,16 +2320,16 @@
         <v>74</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>76</v>
@@ -2350,22 +2338,22 @@
         <v>76</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>81</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>83</v>
@@ -2374,10 +2362,10 @@
         <v>76</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>74</v>
@@ -2386,33 +2374,33 @@
         <v>84</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>73</v>
@@ -2421,16 +2409,16 @@
         <v>74</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>76</v>
@@ -2439,22 +2427,22 @@
         <v>76</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>81</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="V11" s="3" t="s">
         <v>83</v>
@@ -2463,10 +2451,10 @@
         <v>76</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>74</v>
@@ -2475,24 +2463,24 @@
         <v>84</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AC11" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>99</v>
@@ -2501,7 +2489,7 @@
         <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>73</v>
@@ -2531,7 +2519,7 @@
         <v>89</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>105</v>
@@ -2540,7 +2528,7 @@
         <v>81</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>106</v>
@@ -2552,10 +2540,10 @@
         <v>76</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>74</v>
@@ -2564,33 +2552,33 @@
         <v>84</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>73</v>
@@ -2599,16 +2587,16 @@
         <v>74</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>97</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>76</v>
@@ -2620,19 +2608,19 @@
         <v>78</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>81</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>83</v>
@@ -2641,10 +2629,10 @@
         <v>76</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>74</v>
@@ -2653,33 +2641,33 @@
         <v>84</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AC13" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>73</v>
@@ -2688,7 +2676,7 @@
         <v>74</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>76</v>
@@ -2697,7 +2685,7 @@
         <v>76</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>76</v>
@@ -2706,22 +2694,22 @@
         <v>76</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>81</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>83</v>
@@ -2730,10 +2718,10 @@
         <v>76</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>74</v>
@@ -2742,10 +2730,10 @@
         <v>84</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2769,162 +2757,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s">
         <v>8</v>
@@ -2977,7 +2965,7 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -2998,7 +2986,7 @@
         <v>8</v>
       </c>
       <c r="P1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="Q1" t="s">
         <v>8</v>
@@ -3009,106 +2997,106 @@
     </row>
     <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G2" t="s">
         <v>390</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>391</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>392</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>393</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>394</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>395</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>396</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>397</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>398</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>399</v>
       </c>
-      <c r="M2" t="s">
+      <c r="Q2" t="s">
         <v>400</v>
       </c>
-      <c r="N2" t="s">
+      <c r="R2" t="s">
         <v>401</v>
-      </c>
-      <c r="O2" t="s">
-        <v>402</v>
-      </c>
-      <c r="P2" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>404</v>
-      </c>
-      <c r="R2" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="O3" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="Q3" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3116,52 +3104,52 @@
         <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>76</v>
@@ -3172,52 +3160,52 @@
         <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>76</v>
@@ -3228,52 +3216,52 @@
         <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>76</v>
@@ -3284,52 +3272,52 @@
         <v>104</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R7" s="3" t="s">
         <v>76</v>
@@ -3340,52 +3328,52 @@
         <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>76</v>
@@ -3396,52 +3384,52 @@
         <v>116</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>76</v>
@@ -3452,52 +3440,52 @@
         <v>120</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>76</v>
@@ -3505,55 +3493,55 @@
     </row>
     <row r="11" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>76</v>
@@ -3561,55 +3549,55 @@
     </row>
     <row r="12" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>76</v>
@@ -3617,55 +3605,55 @@
     </row>
     <row r="13" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R13" s="3" t="s">
         <v>76</v>
@@ -3673,55 +3661,55 @@
     </row>
     <row r="14" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>76</v>
@@ -3729,55 +3717,55 @@
     </row>
     <row r="15" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>76</v>
@@ -3785,55 +3773,55 @@
     </row>
     <row r="16" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q16" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R16" s="3" t="s">
         <v>76</v>
@@ -3841,55 +3829,55 @@
     </row>
     <row r="17" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>76</v>
@@ -3897,55 +3885,55 @@
     </row>
     <row r="18" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>76</v>
@@ -3953,55 +3941,55 @@
     </row>
     <row r="19" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R19" s="3" t="s">
         <v>76</v>
@@ -4009,55 +3997,55 @@
     </row>
     <row r="20" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>76</v>
@@ -4065,55 +4053,55 @@
     </row>
     <row r="21" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>76</v>
@@ -4121,55 +4109,55 @@
     </row>
     <row r="22" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>76</v>
@@ -4177,55 +4165,55 @@
     </row>
     <row r="23" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>76</v>
@@ -4233,55 +4221,55 @@
     </row>
     <row r="24" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>76</v>
@@ -4310,132 +4298,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4450,207 +4438,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4665,162 +4653,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -4860,7 +4848,7 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -4872,7 +4860,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
@@ -4893,7 +4881,7 @@
         <v>6</v>
       </c>
       <c r="O1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="P1" t="s">
         <v>6</v>
@@ -4913,118 +4901,118 @@
     </row>
     <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" t="s">
         <v>151</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>152</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>153</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>154</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>155</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>156</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>157</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>158</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>159</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>160</v>
       </c>
-      <c r="M2" t="s">
+      <c r="Q2" t="s">
         <v>161</v>
       </c>
-      <c r="N2" t="s">
+      <c r="R2" t="s">
         <v>162</v>
       </c>
-      <c r="O2" t="s">
+      <c r="S2" t="s">
         <v>163</v>
       </c>
-      <c r="P2" t="s">
+      <c r="T2" t="s">
         <v>164</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>165</v>
-      </c>
-      <c r="R2" t="s">
-        <v>166</v>
-      </c>
-      <c r="S2" t="s">
-        <v>167</v>
-      </c>
-      <c r="T2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5032,61 +5020,61 @@
         <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="I4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="O4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5094,61 +5082,61 @@
         <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="N5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5156,61 +5144,61 @@
         <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="I6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="K6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="O6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R6" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="S6" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N6" s="3" t="s">
+      <c r="T6" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5218,61 +5206,61 @@
         <v>104</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="I7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="O7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="Q7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R7" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="S7" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N7" s="3" t="s">
+      <c r="T7" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5280,61 +5268,61 @@
         <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="I8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="K8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="O8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N8" s="3" t="s">
+      <c r="T8" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5342,61 +5330,61 @@
         <v>116</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="I9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="K9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="O9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="S9" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N9" s="3" t="s">
+      <c r="T9" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5404,929 +5392,929 @@
         <v>120</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="I10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="K10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="O10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="Q10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="I11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="K11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="O11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="Q11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="S11" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="I12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="K12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="O12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="S12" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N12" s="3" t="s">
+      <c r="T12" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="K13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="S13" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="N13" s="3" t="s">
+      <c r="T13" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="I14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="K14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="O14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="I15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="K15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="O15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="I16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="K16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N16" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="O16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P16" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="Q16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="S16" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N16" s="3" t="s">
+      <c r="T16" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="I17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="K17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="O17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P17" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="Q17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="T17" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="I18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="K18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="O18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P18" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="Q18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R18" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="S18" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N18" s="3" t="s">
+      <c r="T18" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="I19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="K19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="O19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P19" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="Q19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R19" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="S19" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N19" s="3" t="s">
+      <c r="T19" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="I20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="K20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="O20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P20" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="Q20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R20" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="S20" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N20" s="3" t="s">
+      <c r="T20" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="K21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P21" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="S21" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="N21" s="3" t="s">
+      <c r="T21" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="I22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="K22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="O22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R22" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="S22" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="I23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="K23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="O23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P23" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R23" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="S23" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="I24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="K24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="O24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P24" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R24" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="S24" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N24" s="3" t="s">
+      <c r="T24" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -6352,132 +6340,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -6492,207 +6480,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -6707,162 +6695,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -6887,16 +6875,16 @@
     </row>
     <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6904,10 +6892,10 @@
         <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6915,10 +6903,10 @@
         <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6926,10 +6914,10 @@
         <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6937,10 +6925,10 @@
         <v>104</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6948,10 +6936,10 @@
         <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6959,10 +6947,10 @@
         <v>116</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6970,164 +6958,164 @@
         <v>120</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -7166,7 +7154,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s">
         <v>8</v>
@@ -7178,7 +7166,7 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -7199,7 +7187,7 @@
         <v>6</v>
       </c>
       <c r="P1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="Q1" t="s">
         <v>6</v>
@@ -7207,100 +7195,100 @@
     </row>
     <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G2" t="s">
         <v>346</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>347</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>348</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>349</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>350</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>351</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>352</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>353</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>354</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>355</v>
       </c>
-      <c r="M2" t="s">
+      <c r="Q2" t="s">
         <v>356</v>
-      </c>
-      <c r="N2" t="s">
-        <v>357</v>
-      </c>
-      <c r="O2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P2" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="O3" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7308,52 +7296,52 @@
         <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7361,52 +7349,52 @@
         <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="L5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="P5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7414,52 +7402,52 @@
         <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="L6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="P6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7467,52 +7455,52 @@
         <v>104</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="L7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="P7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7520,52 +7508,52 @@
         <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="L8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="P8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7573,52 +7561,52 @@
         <v>116</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="L9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="P9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7626,794 +7614,794 @@
         <v>120</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="L10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="P10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="L11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="P11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="L12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="P12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="L13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="P13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="L14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="P14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="L15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="P15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="L16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="P16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q16" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="L17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="P17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="L18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="P18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="L19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="P19" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="L20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="P20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="L21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="P21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="L22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="P22" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="L23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="P23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="L24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="P24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -8439,132 +8427,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -8579,207 +8567,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
